--- a/artfynd/A 13586-2025 artfynd.xlsx
+++ b/artfynd/A 13586-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129929606</v>
       </c>
       <c r="B2" t="n">
-        <v>85013</v>
+        <v>85016</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 13586-2025 artfynd.xlsx
+++ b/artfynd/A 13586-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129929606</v>
       </c>
       <c r="B2" t="n">
-        <v>85016</v>
+        <v>85019</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 13586-2025 artfynd.xlsx
+++ b/artfynd/A 13586-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129929606</v>
       </c>
       <c r="B2" t="n">
-        <v>85019</v>
+        <v>85020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 13586-2025 artfynd.xlsx
+++ b/artfynd/A 13586-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129929606</v>
       </c>
       <c r="B2" t="n">
-        <v>85020</v>
+        <v>85024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 13586-2025 artfynd.xlsx
+++ b/artfynd/A 13586-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129929606</v>
       </c>
       <c r="B2" t="n">
-        <v>85032</v>
+        <v>85119</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 13586-2025 artfynd.xlsx
+++ b/artfynd/A 13586-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129929606</v>
       </c>
       <c r="B2" t="n">
-        <v>85119</v>
+        <v>85032</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
